--- a/product_upload/packages/32/file.xlsx
+++ b/product_upload/packages/32/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>TEGRETOL CR 200MG SCORED TAB</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-C956AD862068</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1038,6 +1048,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>FEMARA 2.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-18BC259FE7D0</t>
         </is>
       </c>
@@ -1061,7 +1076,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>GAVISCON DOUBLE ACTION ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-BB49E5DBC236</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1418,6 +1438,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>LESCOL XL 80 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-589308C66301</t>
         </is>
       </c>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1612,6 +1637,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>VOLTAREN SUPP 12.5 MG.</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-CCA791F2B6DC</t>
         </is>
       </c>
@@ -1635,7 +1665,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1798,6 +1828,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ANAFRANIL TAB 10MG</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-B7D011456B12</t>
         </is>
       </c>
@@ -1821,7 +1856,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1980,6 +2015,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ANAFRANIL TABLETS 25 MG</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-5934A71AD14D</t>
         </is>
       </c>
@@ -2003,7 +2043,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2174,6 +2214,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>VIMPAT 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-724B9A54AAA7</t>
         </is>
       </c>
@@ -2197,7 +2242,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2368,6 +2413,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>VIMPAT 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-30895EB3BA18</t>
         </is>
       </c>
@@ -2391,7 +2441,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2562,6 +2612,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FLUTIFORM 50/5 mcg pressurised inhalation suspension</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-CF69B7BD37C3</t>
         </is>
       </c>
@@ -2585,7 +2640,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2760,6 +2815,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>FLUTIFORM 250/10 mcg pressurised inhalation suspension</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-A01487DEA1F6</t>
         </is>
       </c>
@@ -2783,7 +2843,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2942,6 +3002,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>AMARYL 6 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-B05096CDC2DA</t>
         </is>
       </c>
@@ -2965,7 +3030,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3132,6 +3197,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Naselfast nasal spray suspension</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-F3CFF819CA8B</t>
         </is>
       </c>
@@ -3155,7 +3225,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3326,6 +3396,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>FLUTIFORM 125/5 mcg pressurised inhalation suspension</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-9F38052040CF</t>
         </is>
       </c>
@@ -3349,7 +3424,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3512,6 +3587,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>VIRECTA 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-9FD96D60EFF4</t>
         </is>
       </c>
@@ -3535,7 +3615,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3698,6 +3778,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>OCUFENAC 1 mg/ml ophthalmic solution</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-36C4B183C86E</t>
         </is>
       </c>
@@ -3721,7 +3806,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3888,6 +3973,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>XTANDI 40 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-AEE8976E7885</t>
         </is>
       </c>
@@ -3911,7 +4001,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4080,6 +4170,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>SOLIAN 100 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-98C3101B79CD</t>
         </is>
       </c>
@@ -4103,7 +4198,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4272,6 +4367,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>SOLIAN 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-B658899B7424</t>
         </is>
       </c>
@@ -4295,7 +4395,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4468,6 +4568,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SOLIAN 400 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-534D791B453F</t>
         </is>
       </c>
@@ -4491,7 +4596,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4660,6 +4765,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>XATRAL XL 10 MG</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-03C8F1D6B2A3</t>
         </is>
       </c>
@@ -4683,7 +4793,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4856,6 +4966,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CORDARONE 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-D12B4E015EE8</t>
         </is>
       </c>
@@ -4879,7 +4994,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5048,6 +5163,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>DEPAKINE 57.64MG-ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B659332669AB</t>
         </is>
       </c>
@@ -5071,7 +5191,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5236,6 +5356,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>FLAGYL 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-EF78A8ADF4A7</t>
         </is>
       </c>
@@ -5259,7 +5384,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5428,6 +5553,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>FLAGYL 500MG SCORED TABS</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-A4549C97F107</t>
         </is>
       </c>
@@ -5451,7 +5581,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5606,6 +5736,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>10% DEXTROSE in 0.45% SODIUM CHLORIDE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-D8E769EE10E6</t>
         </is>
       </c>
@@ -5629,7 +5764,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5804,6 +5939,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>YAZ PLUS film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-D05604786F67</t>
         </is>
       </c>
@@ -5827,7 +5967,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5998,6 +6138,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CELLCEPT 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-38F234105A92</t>
         </is>
       </c>
@@ -6021,7 +6166,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6196,6 +6341,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>AUBAGIO 14 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-55D5EC8B54E1</t>
         </is>
       </c>
@@ -6219,7 +6369,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6390,6 +6540,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ARIPEX 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-CABF3E31F0D9</t>
         </is>
       </c>
@@ -6413,7 +6568,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6584,6 +6739,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>ARIPEX 5 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-FBB51114D245</t>
         </is>
       </c>
@@ -6607,7 +6767,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6770,6 +6930,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>ARIPEX 15 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-6CD154D02902</t>
         </is>
       </c>
@@ -6793,7 +6958,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6956,6 +7121,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>SOFOCURE 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-321CF95AB579</t>
         </is>
       </c>
@@ -6979,7 +7149,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7142,6 +7312,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>FUSIBACT 2% ointment</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-A6443D8BFAC4</t>
         </is>
       </c>
@@ -7165,7 +7340,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7336,6 +7511,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>OLOPAT 0.1 % ophthalmic solution  - unit dose</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-FC5CAAC81D8D</t>
         </is>
       </c>
@@ -7359,7 +7539,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7526,6 +7706,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>VAROXA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-0944F147D59D</t>
         </is>
       </c>
@@ -7549,7 +7734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7712,6 +7897,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>VAROXA 15 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-9E5E4D3FEB31</t>
         </is>
       </c>
@@ -7735,7 +7925,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7902,6 +8092,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>VAROXA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-4DC15866F4B2</t>
         </is>
       </c>
@@ -7925,7 +8120,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8084,6 +8279,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>VIRECTIL 100 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-0F2DA3BFA40A</t>
         </is>
       </c>
@@ -8107,7 +8307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8266,6 +8466,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>VIRECTIL 100 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-4A7BBBABE6CE</t>
         </is>
       </c>
@@ -8289,7 +8494,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8448,6 +8653,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-BAD3F106053B</t>
         </is>
       </c>
@@ -8471,7 +8681,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8630,6 +8840,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-B6B0050B1479</t>
         </is>
       </c>
@@ -8653,7 +8868,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8820,6 +9035,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>GLUCARE XR 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-AD1AAF3D8B05</t>
         </is>
       </c>
@@ -8843,7 +9063,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9010,6 +9230,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>GLUCARE XR 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-1C10E3390850</t>
         </is>
       </c>
@@ -9033,7 +9258,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9188,6 +9413,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>GLUCARE XR 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-F37E3FA48634</t>
         </is>
       </c>
@@ -9211,7 +9441,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9378,6 +9608,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>GLUCARE XR 750 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-F9CB25E8B7F4</t>
         </is>
       </c>
@@ -9401,7 +9636,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9568,6 +9803,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>GLUCARE XR 750 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-1AF3BBBAA548</t>
         </is>
       </c>
@@ -9591,7 +9831,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9760,6 +10000,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ZOLINDA 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-DC72055CFB2C</t>
         </is>
       </c>
@@ -9783,7 +10028,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9952,6 +10197,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ZOLINDA 5 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-9DE0551736D9</t>
         </is>
       </c>
@@ -9975,7 +10225,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10144,6 +10394,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ZOLINDA 15 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-A47C06821BCE</t>
         </is>
       </c>
@@ -10167,7 +10422,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10338,6 +10593,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>TILCOTIL TAB 20MG</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-717F1098A026</t>
         </is>
       </c>
@@ -10361,7 +10621,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10538,6 +10798,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>REMERON 30MG TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-27671E6177BB</t>
         </is>
       </c>
@@ -10561,7 +10826,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10730,6 +10995,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>COAPROVEL 300-25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-B3DC713E13EB</t>
         </is>
       </c>
@@ -10753,7 +11023,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10918,6 +11188,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>INEGY</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-6D3D1D042204</t>
         </is>
       </c>
@@ -10941,7 +11216,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11110,6 +11385,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>INEGY</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-C55ECAAFC25D</t>
         </is>
       </c>
@@ -11133,7 +11413,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11302,6 +11582,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>EZETROL 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-D3462C94C407</t>
         </is>
       </c>
@@ -11325,7 +11610,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11482,6 +11767,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-112D3CE4BE6D</t>
         </is>
       </c>
@@ -11505,7 +11795,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11664,6 +11954,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-A98B3F8E16CB</t>
         </is>
       </c>
@@ -11687,7 +11982,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11846,6 +12141,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-31D2E46750B0</t>
         </is>
       </c>
@@ -11869,7 +12169,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12028,6 +12328,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-3417015D0547</t>
         </is>
       </c>
@@ -12051,7 +12356,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12206,6 +12511,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-AD31DDBD8F30</t>
         </is>
       </c>
@@ -12229,7 +12539,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12396,6 +12706,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>ESOMEP 20 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-48BC49B52E02</t>
         </is>
       </c>
@@ -12419,7 +12734,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12586,6 +12901,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ESOMEP 40 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-87DC5D7FA538</t>
         </is>
       </c>
@@ -12609,7 +12929,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12784,6 +13104,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ESOMEP 40 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-CF9AE8981DDD</t>
         </is>
       </c>
@@ -12807,7 +13132,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12978,6 +13303,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>KEMADRIN 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-97DAEA19009D</t>
         </is>
       </c>
@@ -13001,7 +13331,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13176,6 +13506,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ALKERAN TABLETS 2 MG</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-E3A21561F1CD</t>
         </is>
       </c>
@@ -13199,7 +13534,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13362,6 +13697,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>DICERAN 8 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-98471F6200EB</t>
         </is>
       </c>
@@ -13385,7 +13725,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13548,6 +13888,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>DICERAN 16 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-CEDE1305C42A</t>
         </is>
       </c>
@@ -13571,7 +13916,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13734,6 +14079,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>MEMENTA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-04AF34B80B5D</t>
         </is>
       </c>
@@ -13757,7 +14107,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13932,6 +14282,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>ESOMEP 20 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-1F4AE803A3BD</t>
         </is>
       </c>
@@ -13955,7 +14310,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14116,6 +14471,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-269BA43B4F68</t>
         </is>
       </c>
@@ -14139,7 +14499,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14312,6 +14672,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>SINGULAIR</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-593A3673947E</t>
         </is>
       </c>
@@ -14335,7 +14700,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14504,6 +14869,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>SINGULAIR PAEDIATRIC 4 MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-84713D899C37</t>
         </is>
       </c>
@@ -14527,7 +14897,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14698,6 +15068,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>VIMPAT 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-F0CE2B06B546</t>
         </is>
       </c>
@@ -14721,7 +15096,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14892,6 +15267,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>GOUTEX 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-FDDCFE51B661</t>
         </is>
       </c>
@@ -14915,7 +15295,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15078,6 +15458,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>GOUTEX 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-1AC89459D031</t>
         </is>
       </c>
@@ -15101,7 +15486,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15272,6 +15657,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>TRESIBA FlexTouch 100 U/ml solution for injection</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-BFAEB518CBEB</t>
         </is>
       </c>
@@ -15295,7 +15685,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15462,6 +15852,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>SOVIRA 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-0ACB8ABAE9B7</t>
         </is>
       </c>
@@ -15485,7 +15880,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15656,6 +16051,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>GABEX 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-774868FAD5DA</t>
         </is>
       </c>
@@ -15679,7 +16079,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15846,6 +16246,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>GABEX 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-B587693CB5BF</t>
         </is>
       </c>
@@ -15869,7 +16274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16040,6 +16445,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>GABEX 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-94F6830FC5AC</t>
         </is>
       </c>
@@ -16063,7 +16473,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,6 +16642,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>SPRYCEL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-83BEFCCEA2A3</t>
         </is>
       </c>
@@ -16255,7 +16670,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16424,6 +16839,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>SPRYCEL 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-582800A5E886</t>
         </is>
       </c>
@@ -16447,7 +16867,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16616,6 +17036,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>SPRYCEL 70MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-682BEDE6E60A</t>
         </is>
       </c>
@@ -16639,7 +17064,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16810,6 +17235,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>VALES 100 mg/ml oral solutin</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-2C8D0C6AF846</t>
         </is>
       </c>
@@ -16833,7 +17263,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17002,6 +17432,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>SINGULAIR</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-648F83305FD6</t>
         </is>
       </c>
@@ -17025,7 +17460,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17196,6 +17631,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>LAVISTINA 24 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-4DD99F153CC1</t>
         </is>
       </c>
@@ -17219,7 +17659,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17390,6 +17830,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>LAVISTINA 8 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-A9D743DA2F3D</t>
         </is>
       </c>
@@ -17413,7 +17858,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17578,6 +18023,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>SINGULAIR PEDIATRIC 4MG GRANULES</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-569EC797315E</t>
         </is>
       </c>
@@ -17601,7 +18051,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17770,6 +18220,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>JANUVIA 100MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-0844F4BF6933</t>
         </is>
       </c>
@@ -17793,7 +18248,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17962,6 +18417,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>PROSCAR</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-78AFB010D706</t>
         </is>
       </c>
@@ -17985,7 +18445,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18154,6 +18614,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>JANUMET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-ABB0AA5ACC11</t>
         </is>
       </c>
@@ -18177,7 +18642,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18346,6 +18811,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>JANUMET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FBDFE222BAB2</t>
         </is>
       </c>
@@ -18369,7 +18839,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18538,6 +19008,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ZOCOR 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-20959E59343A</t>
         </is>
       </c>
@@ -18561,7 +19036,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18730,6 +19205,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ZOCOR 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-0D2A8983CE43</t>
         </is>
       </c>
@@ -18753,7 +19233,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18922,6 +19402,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>ZOCOR 40MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-6D79E5471362</t>
         </is>
       </c>
@@ -18945,7 +19430,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19114,6 +19599,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>NASONEX 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-BC480BBE5263</t>
         </is>
       </c>
@@ -19137,7 +19627,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19310,6 +19800,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ATROVENT 250MCG-2ML UDV (SOLUTION FOR INHALATION)</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-95B3D3932AC0</t>
         </is>
       </c>
@@ -19333,7 +19828,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19504,6 +19999,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>LAVISTINA 16 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-1CA491FB147D</t>
         </is>
       </c>
@@ -19527,7 +20027,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19703,6 +20203,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ATROVENT 500MCG-2ML UDV (SOLUTION FOR INHALATION)</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-12E231BC22D0</t>
         </is>
@@ -19719,7 +20224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19765,100 +20270,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19890,7 +20400,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19905,92 +20415,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-73712</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>263.13</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>264</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20022,7 +20537,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20037,92 +20552,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-34253</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>294.78</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>265</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20154,7 +20674,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20169,92 +20689,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-91917</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>296.17</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>266</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20286,7 +20811,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20301,92 +20826,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-31805</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>190.36</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>267</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20418,7 +20948,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20433,92 +20963,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-94947</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>273.79</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>268</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20550,7 +21085,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20565,92 +21100,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-48428</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>89.14</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>269</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20682,7 +21222,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20697,92 +21237,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-79561</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>147.36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>270</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20814,7 +21359,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20829,92 +21374,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-77097</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>391.91</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>271</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20946,7 +21496,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20961,92 +21511,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-75121</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>395.99</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>272</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21078,7 +21633,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21093,92 +21648,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-31645</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>180.85</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>273</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21210,7 +21770,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21225,92 +21785,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-25187</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>443.94</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>274</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21327,7 +21892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21433,6 +21998,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21468,7 +22043,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21533,6 +22108,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-49449202BA80</t>
         </is>
@@ -21569,7 +22154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21634,6 +22219,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-511961581C81</t>
         </is>
@@ -21670,7 +22265,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21735,6 +22330,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-38B775965F62</t>
         </is>
@@ -21771,7 +22376,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21836,6 +22441,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-E796226EB463</t>
         </is>
@@ -21872,7 +22487,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21937,6 +22552,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-4F1734B06B2C</t>
         </is>
@@ -21973,7 +22598,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22038,6 +22663,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-9BBD8E56C2F0</t>
         </is>
@@ -22074,7 +22709,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22139,6 +22774,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-274EF6103802</t>
         </is>
@@ -22175,7 +22820,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22240,6 +22885,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-B9A3193F7D70</t>
         </is>
@@ -22276,7 +22931,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22341,6 +22996,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-DDC45C6DA4E2</t>
         </is>
@@ -22377,7 +23042,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22442,6 +23107,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-8CD6386D7B9A</t>
         </is>
@@ -22478,7 +23153,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22543,6 +23218,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-6CAE046EF697</t>
         </is>
@@ -22579,7 +23264,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22644,6 +23329,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F118A27BE242</t>
         </is>
@@ -22680,7 +23375,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22745,6 +23440,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-BEFCBB976A42</t>
         </is>
@@ -22781,7 +23486,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22846,6 +23551,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-FC38BE045FC7</t>
         </is>
@@ -22882,7 +23597,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22947,6 +23662,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A556F9361F52</t>
         </is>
@@ -22983,7 +23708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23048,6 +23773,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-17CED3B37422</t>
         </is>
@@ -23084,7 +23819,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23149,6 +23884,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-DAD17D981920</t>
         </is>
@@ -23185,7 +23930,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23250,6 +23995,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-BC09DB11FD9A</t>
         </is>
@@ -23286,7 +24041,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23351,6 +24106,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-7EF09AA6DF75</t>
         </is>
@@ -23387,7 +24152,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23452,6 +24217,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-B3741EFC34AB</t>
         </is>

--- a/product_upload/packages/32/file.xlsx
+++ b/product_upload/packages/32/file.xlsx
@@ -1084,8 +1084,16 @@
           <t>4569415682-979-957412890405</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVISCON DOUBLE ACTION ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GAVISCON DOUBLE ACTION ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1673,8 +1681,16 @@
           <t>8696562096-646-199280281787</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANAFRANIL TAB 10MG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ANAFRANIL TAB 10MG detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1864,8 +1880,16 @@
           <t>8814891754-570-503258587637</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANAFRANIL TABLETS 25 MG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ANAFRANIL TABLETS 25 MG detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2851,8 +2875,16 @@
           <t>3305118815-684-367676693537</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMARYL 6 mg tablet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AMARYL 6 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3432,8 +3464,16 @@
           <t>3376590220-213-409842903348</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTA 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>VIRECTA 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3623,8 +3663,16 @@
           <t>8875056246-724-767282597020</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OCUFENAC 1 mg/ml ophthalmic solution</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OCUFENAC 1 mg/ml ophthalmic solution detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -5589,8 +5637,16 @@
           <t>0024120541-383-150590500024</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 10% DEXTROSE in 0.45% SODIUM CHLORIDE intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10% DEXTROSE in 0.45% SODIUM CHLORIDE intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -6966,8 +7022,16 @@
           <t>2086228291-264-938096809241</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOFOCURE 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SOFOCURE 400 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -8128,8 +8192,16 @@
           <t>3038678953-768-279093951711</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTIL 100 mg tablet</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VIRECTIL 100 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8315,8 +8387,16 @@
           <t>2012859436-281-745730998020</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTIL 100 mg tablet</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VIRECTIL 100 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8502,8 +8582,16 @@
           <t>5049304656-140-466080414904</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VIRECTIL 50 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8689,8 +8777,16 @@
           <t>9637110197-406-750798827935</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VIRECTIL 50 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -9266,8 +9362,16 @@
           <t>3046765293-970-295805567150</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCARE XR 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>GLUCARE XR 500 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -10430,8 +10534,16 @@
           <t>0694942014-572-108399007186</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TILCOTIL TAB 20MG</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TILCOTIL TAB 20MG detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -11618,8 +11730,16 @@
           <t>5612304137-374-485818748941</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11803,8 +11923,16 @@
           <t>3787524868-428-130075589492</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11990,8 +12118,16 @@
           <t>2756339855-051-513811880351</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12177,8 +12313,16 @@
           <t>7488190162-190-538754431929</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12364,8 +12508,16 @@
           <t>4177565563-771-576451127404</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5 and 5% dextrose solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12547,8 +12699,16 @@
           <t>3339445466-255-430945824447</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMEP 20 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ESOMEP 20 mg gastro-resistant tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12742,8 +12902,16 @@
           <t>3459729766-869-183755680176</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOMEP 40 mg gastro-resistant tablet</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ESOMEP 40 mg gastro-resistant tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13542,8 +13710,16 @@
           <t>2776075023-558-120548331951</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICERAN 8 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DICERAN 8 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13733,8 +13909,16 @@
           <t>2411779329-808-341702186516</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICERAN 16 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DICERAN 16 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13924,8 +14108,16 @@
           <t>6275177687-909-281486769471</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MEMENTA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MEMENTA 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14318,8 +14510,16 @@
           <t>4031854961-105-771540913231</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 5.5 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 5.5 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/32/file.xlsx
+++ b/product_upload/packages/32/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22092,7 +22092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22173,40 +22173,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22286,38 +22291,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>119.05</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-49449202BA80</t>
         </is>
@@ -22397,38 +22407,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>78.56</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-511961581C81</t>
         </is>
@@ -22508,38 +22523,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>388.42</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-38B775965F62</t>
         </is>
@@ -22619,38 +22639,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>61.12</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-E796226EB463</t>
         </is>
@@ -22730,38 +22755,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>209.28</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-4F1734B06B2C</t>
         </is>
@@ -22841,38 +22871,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>459.86</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-9BBD8E56C2F0</t>
         </is>
@@ -22952,38 +22987,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>142.85</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-274EF6103802</t>
         </is>
@@ -23063,38 +23103,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>22.58</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-B9A3193F7D70</t>
         </is>
@@ -23174,38 +23219,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>176.39</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-DDC45C6DA4E2</t>
         </is>
@@ -23285,38 +23335,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>328.1</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-8CD6386D7B9A</t>
         </is>
@@ -23396,38 +23451,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>273.19</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-6CAE046EF697</t>
         </is>
@@ -23507,38 +23567,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>482.27</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F118A27BE242</t>
         </is>
@@ -23618,38 +23683,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>370.38</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-BEFCBB976A42</t>
         </is>
@@ -23729,38 +23799,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>256.3</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-FC38BE045FC7</t>
         </is>
@@ -23840,38 +23915,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>449.15</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A556F9361F52</t>
         </is>
@@ -23951,38 +24031,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>109.53</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-17CED3B37422</t>
         </is>
@@ -24062,38 +24147,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>419.61</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-DAD17D981920</t>
         </is>
@@ -24173,38 +24263,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>104.18</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-BC09DB11FD9A</t>
         </is>
@@ -24284,38 +24379,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>483.95</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-7EF09AA6DF75</t>
         </is>
@@ -24395,38 +24495,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>193.03</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-B3741EFC34AB</t>
         </is>
